--- a/docs/configs/GameConfig.xlsx
+++ b/docs/configs/GameConfig.xlsx
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="C1" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="D1" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1044,6 +1044,86 @@
       <c r="D15" t="inlineStr">
         <is>
           <t>每3级+HP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CRAWLER_SPEED</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>爬行僵尸速度 px/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CRAWLER_HP_BASE</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>爬行僵尸基础血量(脆皮)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CRAWLER_SPAWN_LEVEL</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>爬行僵尸最低出现关卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CRAWLER_CHANCE</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>爬行僵尸生成概率</t>
         </is>
       </c>
     </row>
